--- a/upload/valores_naorealizados_2025.xlsx
+++ b/upload/valores_naorealizados_2025.xlsx
@@ -1272,13 +1272,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1311,6 +1304,13 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1354,7 +1354,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:Q313" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" headerRowBorderDxfId="18" tableBorderDxfId="19" totalsRowBorderDxfId="17" headerRowCellStyle="Moeda" dataCellStyle="Moeda">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:Q313" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17" headerRowCellStyle="Moeda" dataCellStyle="Moeda">
   <sortState ref="A2:Q371">
     <sortCondition ref="E1:E371"/>
   </sortState>
